--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/40.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/40.xlsx
@@ -426,13 +426,13 @@
         <v>-12.08172186714482</v>
       </c>
       <c r="E2">
-        <v>-17.36531871155108</v>
+        <v>-12.53335543283467</v>
       </c>
       <c r="F2">
-        <v>-4.42247064159805</v>
+        <v>-4.453027458352517</v>
       </c>
       <c r="G2">
-        <v>-10.75514590301222</v>
+        <v>-8.369073516128053</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.76869599305171</v>
       </c>
       <c r="E3">
-        <v>-17.79008051652255</v>
+        <v>-13.10389787306106</v>
       </c>
       <c r="F3">
-        <v>-5.004127037556584</v>
+        <v>-4.317861092502917</v>
       </c>
       <c r="G3">
-        <v>-11.4942748528376</v>
+        <v>-7.767037567629429</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.26764195421113</v>
       </c>
       <c r="E4">
-        <v>-17.16620170943382</v>
+        <v>-13.47247942949337</v>
       </c>
       <c r="F4">
-        <v>-4.656930094551616</v>
+        <v>-4.45815919441286</v>
       </c>
       <c r="G4">
-        <v>-10.92251053275008</v>
+        <v>-7.561657943464123</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-10.6103426628389</v>
       </c>
       <c r="E5">
-        <v>-18.64303218128928</v>
+        <v>-14.84793095373912</v>
       </c>
       <c r="F5">
-        <v>-4.843525650604025</v>
+        <v>-4.532078559601675</v>
       </c>
       <c r="G5">
-        <v>-9.94556523356561</v>
+        <v>-7.118024977928549</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-9.807163024638776</v>
       </c>
       <c r="E6">
-        <v>-19.02499084994025</v>
+        <v>-15.5488843884384</v>
       </c>
       <c r="F6">
-        <v>-4.512476073381827</v>
+        <v>-4.379689607080469</v>
       </c>
       <c r="G6">
-        <v>-9.574837101895865</v>
+        <v>-6.763627767404029</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.892872177163873</v>
       </c>
       <c r="E7">
-        <v>-19.2736946424415</v>
+        <v>-15.98556060852404</v>
       </c>
       <c r="F7">
-        <v>-4.399101568797673</v>
+        <v>-3.857012141833857</v>
       </c>
       <c r="G7">
-        <v>-10.24583502452304</v>
+        <v>-6.318779831655542</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.896454448847016</v>
       </c>
       <c r="E8">
-        <v>-19.42548909117861</v>
+        <v>-16.15973477580706</v>
       </c>
       <c r="F8">
-        <v>-4.473715105870032</v>
+        <v>-4.035295859366575</v>
       </c>
       <c r="G8">
-        <v>-10.58061725272738</v>
+        <v>-5.613391961966412</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.842898111301074</v>
       </c>
       <c r="E9">
-        <v>-19.84324534686021</v>
+        <v>-17.10810591638942</v>
       </c>
       <c r="F9">
-        <v>-4.437964425500011</v>
+        <v>-4.261334129303282</v>
       </c>
       <c r="G9">
-        <v>-9.614348462907065</v>
+        <v>-5.976184715978524</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.756442944819986</v>
       </c>
       <c r="E10">
-        <v>-20.32362134111987</v>
+        <v>-17.96773708031746</v>
       </c>
       <c r="F10">
-        <v>-4.143530344216358</v>
+        <v>-3.904151217257565</v>
       </c>
       <c r="G10">
-        <v>-9.116415929436366</v>
+        <v>-5.238277357457133</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.670715548873287</v>
       </c>
       <c r="E11">
-        <v>-20.85641895049233</v>
+        <v>-18.49053581908098</v>
       </c>
       <c r="F11">
-        <v>-4.419392428329247</v>
+        <v>-3.99852048851929</v>
       </c>
       <c r="G11">
-        <v>-8.993942297211028</v>
+        <v>-5.695652397526223</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.611222291086453</v>
       </c>
       <c r="E12">
-        <v>-23.09891022214268</v>
+        <v>-18.26810623277223</v>
       </c>
       <c r="F12">
-        <v>-3.680220313993581</v>
+        <v>-3.993136928768497</v>
       </c>
       <c r="G12">
-        <v>-7.535713198072855</v>
+        <v>-4.688485128113749</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.601009626148263</v>
       </c>
       <c r="E13">
-        <v>-23.18420403007715</v>
+        <v>-19.17358819602794</v>
       </c>
       <c r="F13">
-        <v>-4.111180112034829</v>
+        <v>-3.957634758619315</v>
       </c>
       <c r="G13">
-        <v>-7.838568525096462</v>
+        <v>-4.724192672300329</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.680758315949659</v>
       </c>
       <c r="E14">
-        <v>-22.08376220384321</v>
+        <v>-19.84029731028122</v>
       </c>
       <c r="F14">
-        <v>-3.958751397878289</v>
+        <v>-3.682817245801357</v>
       </c>
       <c r="G14">
-        <v>-7.172102739312543</v>
+        <v>-4.255793515585466</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-0.8790627742808583</v>
       </c>
       <c r="E15">
-        <v>-23.72718164901885</v>
+        <v>-20.58749099307282</v>
       </c>
       <c r="F15">
-        <v>-3.919359214405561</v>
+        <v>-3.39375264202265</v>
       </c>
       <c r="G15">
-        <v>-6.223889664863412</v>
+        <v>-4.020062809916122</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.2168304991406394</v>
       </c>
       <c r="E16">
-        <v>-24.2292173344572</v>
+        <v>-21.8759369462092</v>
       </c>
       <c r="F16">
-        <v>-3.523727629358906</v>
+        <v>-3.019888067219358</v>
       </c>
       <c r="G16">
-        <v>-6.967789110810883</v>
+        <v>-3.22665415542885</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>0.2822461518198933</v>
       </c>
       <c r="E17">
-        <v>-25.28201508565643</v>
+        <v>-22.25838016157898</v>
       </c>
       <c r="F17">
-        <v>-3.664678484782256</v>
+        <v>-2.915428452624131</v>
       </c>
       <c r="G17">
-        <v>-5.593939196377654</v>
+        <v>-2.608836836344522</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>0.6127478083689574</v>
       </c>
       <c r="E18">
-        <v>-26.00996728238944</v>
+        <v>-22.67211966081577</v>
       </c>
       <c r="F18">
-        <v>-3.31591095718158</v>
+        <v>-2.613589595126853</v>
       </c>
       <c r="G18">
-        <v>-5.57947211237104</v>
+        <v>-2.877874940684473</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.7871431371951018</v>
       </c>
       <c r="E19">
-        <v>-25.88500404214778</v>
+        <v>-23.4010817072525</v>
       </c>
       <c r="F19">
-        <v>-2.661827085726674</v>
+        <v>-2.596140035786882</v>
       </c>
       <c r="G19">
-        <v>-6.10834169390623</v>
+        <v>-2.053406747947759</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.8262326412422306</v>
       </c>
       <c r="E20">
-        <v>-27.1959112263622</v>
+        <v>-23.91928857337224</v>
       </c>
       <c r="F20">
-        <v>-2.543190791399937</v>
+        <v>-2.293133180251656</v>
       </c>
       <c r="G20">
-        <v>-5.196862432760851</v>
+        <v>-1.346284152396051</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.7617219700102791</v>
       </c>
       <c r="E21">
-        <v>-28.11908593756588</v>
+        <v>-25.14272828212851</v>
       </c>
       <c r="F21">
-        <v>-2.450093064101509</v>
+        <v>-1.86147589685725</v>
       </c>
       <c r="G21">
-        <v>-5.248321552623282</v>
+        <v>-2.535312930462848</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.6339818049971797</v>
       </c>
       <c r="E22">
-        <v>-28.65599992981131</v>
+        <v>-25.71884980233235</v>
       </c>
       <c r="F22">
-        <v>-2.332277681870947</v>
+        <v>-1.691349941507302</v>
       </c>
       <c r="G22">
-        <v>-5.064106246090537</v>
+        <v>-1.829809191679844</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.4840387680182834</v>
       </c>
       <c r="E23">
-        <v>-28.04118259921193</v>
+        <v>-25.15260488393924</v>
       </c>
       <c r="F23">
-        <v>-2.71487159236494</v>
+        <v>-1.421631858420977</v>
       </c>
       <c r="G23">
-        <v>-5.364455490140915</v>
+        <v>-2.142824582963474</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.3500509184630065</v>
       </c>
       <c r="E24">
-        <v>-30.50175838636067</v>
+        <v>-26.38275579117487</v>
       </c>
       <c r="F24">
-        <v>-2.604690444118578</v>
+        <v>-1.358201281286411</v>
       </c>
       <c r="G24">
-        <v>-5.879334706227145</v>
+        <v>-2.329363892464787</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>0.2662036379150916</v>
       </c>
       <c r="E25">
-        <v>-30.78352456759193</v>
+        <v>-26.73248531031325</v>
       </c>
       <c r="F25">
-        <v>-2.0388517237165</v>
+        <v>-1.373826775605418</v>
       </c>
       <c r="G25">
-        <v>-4.350723408924067</v>
+        <v>-2.17881683406643</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>0.2581332068324088</v>
       </c>
       <c r="E26">
-        <v>-30.73112559484917</v>
+        <v>-27.07558514350439</v>
       </c>
       <c r="F26">
-        <v>-2.423825533758737</v>
+        <v>-1.391762586610833</v>
       </c>
       <c r="G26">
-        <v>-5.547624664283251</v>
+        <v>-2.290762931476885</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>0.3453003804305018</v>
       </c>
       <c r="E27">
-        <v>-28.65496743773756</v>
+        <v>-26.55022328845253</v>
       </c>
       <c r="F27">
-        <v>-2.726749552553682</v>
+        <v>-1.350099848087032</v>
       </c>
       <c r="G27">
-        <v>-6.041220383097506</v>
+        <v>-2.936143852721185</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.5370808762093835</v>
       </c>
       <c r="E28">
-        <v>-31.26957021130919</v>
+        <v>-27.32885363780538</v>
       </c>
       <c r="F28">
-        <v>-1.674309595664313</v>
+        <v>-1.151801117367872</v>
       </c>
       <c r="G28">
-        <v>-5.842984916205947</v>
+        <v>-2.553871848756002</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>0.8294879349497656</v>
       </c>
       <c r="E29">
-        <v>-30.22728757675577</v>
+        <v>-27.20891700371223</v>
       </c>
       <c r="F29">
-        <v>-1.954630781506472</v>
+        <v>-1.187986690624363</v>
       </c>
       <c r="G29">
-        <v>-4.592519034021356</v>
+        <v>-2.732585028602478</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.217652567001323</v>
       </c>
       <c r="E30">
-        <v>-30.07572634443005</v>
+        <v>-27.08927924890359</v>
       </c>
       <c r="F30">
-        <v>-2.101207908329636</v>
+        <v>-1.233383709399984</v>
       </c>
       <c r="G30">
-        <v>-5.595342867686306</v>
+        <v>-2.828369042690212</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.687916453523918</v>
       </c>
       <c r="E31">
-        <v>-29.49074712906721</v>
+        <v>-26.50990175588824</v>
       </c>
       <c r="F31">
-        <v>-1.784749194540349</v>
+        <v>-1.184166260162651</v>
       </c>
       <c r="G31">
-        <v>-6.656664041030177</v>
+        <v>-2.571755415759145</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>2.215655141188817</v>
       </c>
       <c r="E32">
-        <v>-29.8349949304193</v>
+        <v>-26.9556802087293</v>
       </c>
       <c r="F32">
-        <v>-1.638982211037123</v>
+        <v>-1.093575172625095</v>
       </c>
       <c r="G32">
-        <v>-6.318677204743825</v>
+        <v>-3.456286836214856</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>2.780737843720043</v>
       </c>
       <c r="E33">
-        <v>-29.00966922133636</v>
+        <v>-25.99298097638667</v>
       </c>
       <c r="F33">
-        <v>-2.312644546057196</v>
+        <v>-1.204809175840415</v>
       </c>
       <c r="G33">
-        <v>-4.979773409023142</v>
+        <v>-3.412359207454267</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>3.361364294569553</v>
       </c>
       <c r="E34">
-        <v>-29.70288802243054</v>
+        <v>-25.94401005846773</v>
       </c>
       <c r="F34">
-        <v>-2.369669358065913</v>
+        <v>-1.514366760796979</v>
       </c>
       <c r="G34">
-        <v>-5.603076302066043</v>
+        <v>-2.595826392375186</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>3.931702760482409</v>
       </c>
       <c r="E35">
-        <v>-28.35288199363389</v>
+        <v>-25.46000222805391</v>
       </c>
       <c r="F35">
-        <v>-2.380828295349026</v>
+        <v>-1.255658508861263</v>
       </c>
       <c r="G35">
-        <v>-6.483499335507519</v>
+        <v>-3.397597484894657</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.471083764014314</v>
       </c>
       <c r="E36">
-        <v>-28.9468185305839</v>
+        <v>-24.26503756385787</v>
       </c>
       <c r="F36">
-        <v>-2.432723856399609</v>
+        <v>-1.449753275011215</v>
       </c>
       <c r="G36">
-        <v>-5.881890447383462</v>
+        <v>-3.223466100074531</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.96502481910587</v>
       </c>
       <c r="E37">
-        <v>-26.62506990685131</v>
+        <v>-24.46462099879793</v>
       </c>
       <c r="F37">
-        <v>-2.16894599595876</v>
+        <v>-1.250791022002413</v>
       </c>
       <c r="G37">
-        <v>-5.602847874423833</v>
+        <v>-3.454869922724048</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.398924815904355</v>
       </c>
       <c r="E38">
-        <v>-27.37726755342138</v>
+        <v>-23.78710694556235</v>
       </c>
       <c r="F38">
-        <v>-2.088224906025559</v>
+        <v>-1.269422661626179</v>
       </c>
       <c r="G38">
-        <v>-5.244084054333014</v>
+        <v>-3.518435707623595</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.760495901071327</v>
       </c>
       <c r="E39">
-        <v>-25.78497910826636</v>
+        <v>-23.43102397739121</v>
       </c>
       <c r="F39">
-        <v>-2.72961901723698</v>
+        <v>-1.341841853448523</v>
       </c>
       <c r="G39">
-        <v>-6.85070173617794</v>
+        <v>-2.899860273610773</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>6.047302671561193</v>
       </c>
       <c r="E40">
-        <v>-25.38585752312632</v>
+        <v>-22.42924401436239</v>
       </c>
       <c r="F40">
-        <v>-2.092206868130816</v>
+        <v>-1.257063419976411</v>
       </c>
       <c r="G40">
-        <v>-6.795455352218582</v>
+        <v>-3.605734793494176</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>6.257340454116453</v>
       </c>
       <c r="E41">
-        <v>-25.70057288123739</v>
+        <v>-22.30961984497577</v>
       </c>
       <c r="F41">
-        <v>-2.317121043501924</v>
+        <v>-1.001283446809591</v>
       </c>
       <c r="G41">
-        <v>-6.895238505317755</v>
+        <v>-2.703207247486986</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>6.387314384354683</v>
       </c>
       <c r="E42">
-        <v>-24.71495957041595</v>
+        <v>-21.3139487933833</v>
       </c>
       <c r="F42">
-        <v>-2.14384812038874</v>
+        <v>-1.060204391803317</v>
       </c>
       <c r="G42">
-        <v>-5.751567511684513</v>
+        <v>-3.100767350752524</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>6.444601546961112</v>
       </c>
       <c r="E43">
-        <v>-24.97880657999886</v>
+        <v>-20.36825850941348</v>
       </c>
       <c r="F43">
-        <v>-2.112809193805843</v>
+        <v>-1.264695997225805</v>
       </c>
       <c r="G43">
-        <v>-6.317935642543028</v>
+        <v>-3.242240203827738</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>6.435498439620344</v>
       </c>
       <c r="E44">
-        <v>-24.77168776431004</v>
+        <v>-21.24305553279322</v>
       </c>
       <c r="F44">
-        <v>-2.370057862377827</v>
+        <v>-1.34553968553462</v>
       </c>
       <c r="G44">
-        <v>-6.117594668688493</v>
+        <v>-2.843859085268462</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>6.361874888099015</v>
       </c>
       <c r="E45">
-        <v>-23.35549355941728</v>
+        <v>-20.05278689614313</v>
       </c>
       <c r="F45">
-        <v>-2.115126965798876</v>
+        <v>-1.178322128135901</v>
       </c>
       <c r="G45">
-        <v>-6.192091874958712</v>
+        <v>-2.933094840279517</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>6.231705125331835</v>
       </c>
       <c r="E46">
-        <v>-21.84589957811632</v>
+        <v>-19.38240066099563</v>
       </c>
       <c r="F46">
-        <v>-2.271294930411653</v>
+        <v>-1.38959889095472</v>
       </c>
       <c r="G46">
-        <v>-6.295841061613932</v>
+        <v>-3.387692332641158</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>6.054015582631766</v>
       </c>
       <c r="E47">
-        <v>-22.17938546098918</v>
+        <v>-18.63788330634256</v>
       </c>
       <c r="F47">
-        <v>-2.023665264120977</v>
+        <v>-1.127428891642705</v>
       </c>
       <c r="G47">
-        <v>-5.799209572540165</v>
+        <v>-3.140056905212594</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.833097031303279</v>
       </c>
       <c r="E48">
-        <v>-21.95610452156698</v>
+        <v>-18.38660734060495</v>
       </c>
       <c r="F48">
-        <v>-1.868090410568604</v>
+        <v>-1.171450820529679</v>
       </c>
       <c r="G48">
-        <v>-6.945823641157819</v>
+        <v>-3.367302682664786</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.573761720282285</v>
       </c>
       <c r="E49">
-        <v>-21.17958896957572</v>
+        <v>-17.65647241940024</v>
       </c>
       <c r="F49">
-        <v>-2.005235746143494</v>
+        <v>-1.414290866497368</v>
       </c>
       <c r="G49">
-        <v>-5.580822814951063</v>
+        <v>-3.106832270180468</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.28581069927742</v>
       </c>
       <c r="E50">
-        <v>-19.86168076454544</v>
+        <v>-17.1242725685968</v>
       </c>
       <c r="F50">
-        <v>-1.936353683131103</v>
+        <v>-1.26032387407383</v>
       </c>
       <c r="G50">
-        <v>-6.714472787236931</v>
+        <v>-3.512023180914026</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.971832578860705</v>
       </c>
       <c r="E51">
-        <v>-21.47250878228787</v>
+        <v>-17.12503335223009</v>
       </c>
       <c r="F51">
-        <v>-2.005480942894722</v>
+        <v>-1.141429129117419</v>
       </c>
       <c r="G51">
-        <v>-7.30439544960736</v>
+        <v>-3.105594126148781</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.630229008833357</v>
       </c>
       <c r="E52">
-        <v>-20.49259229176808</v>
+        <v>-16.31215415395723</v>
       </c>
       <c r="F52">
-        <v>-1.789282849335871</v>
+        <v>-1.072002000353987</v>
       </c>
       <c r="G52">
-        <v>-5.708354960760406</v>
+        <v>-3.254105199040486</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.267043640067723</v>
       </c>
       <c r="E53">
-        <v>-17.97722876183754</v>
+        <v>-14.6986135802842</v>
       </c>
       <c r="F53">
-        <v>-2.060327148634078</v>
+        <v>-1.287261553645467</v>
       </c>
       <c r="G53">
-        <v>-6.258564318841738</v>
+        <v>-3.196799655755702</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.881935694072166</v>
       </c>
       <c r="E54">
-        <v>-18.74112345676943</v>
+        <v>-15.34301543157569</v>
       </c>
       <c r="F54">
-        <v>-2.141268584296423</v>
+        <v>-1.160065738945603</v>
       </c>
       <c r="G54">
-        <v>-7.489180169972859</v>
+        <v>-3.677725916791167</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.472317838703968</v>
       </c>
       <c r="E55">
-        <v>-18.74613647749592</v>
+        <v>-15.04419048875754</v>
       </c>
       <c r="F55">
-        <v>-2.351132152326066</v>
+        <v>-1.264670317836319</v>
       </c>
       <c r="G55">
-        <v>-6.835311009965868</v>
+        <v>-3.429127120610675</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.041922963813491</v>
       </c>
       <c r="E56">
-        <v>-16.44276892976046</v>
+        <v>-14.3933853752192</v>
       </c>
       <c r="F56">
-        <v>-1.789829571821718</v>
+        <v>-1.050226706436597</v>
       </c>
       <c r="G56">
-        <v>-7.839608036395793</v>
+        <v>-3.588496782871191</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>2.593672421367118</v>
       </c>
       <c r="E57">
-        <v>-18.42439292772495</v>
+        <v>-14.56461150592323</v>
       </c>
       <c r="F57">
-        <v>-2.31277625647424</v>
+        <v>-1.420241029551677</v>
       </c>
       <c r="G57">
-        <v>-6.227140620582976</v>
+        <v>-3.691497786234535</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.129990807634187</v>
       </c>
       <c r="E58">
-        <v>-17.16703947712524</v>
+        <v>-13.38147521583523</v>
       </c>
       <c r="F58">
-        <v>-2.404672022671206</v>
+        <v>-1.60997444132589</v>
       </c>
       <c r="G58">
-        <v>-6.705630320101537</v>
+        <v>-3.873051414153706</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>1.658273811864905</v>
       </c>
       <c r="E59">
-        <v>-17.30061587492949</v>
+        <v>-13.45117295928728</v>
       </c>
       <c r="F59">
-        <v>-2.92992985237754</v>
+        <v>-1.271680791166211</v>
       </c>
       <c r="G59">
-        <v>-7.612825735319099</v>
+        <v>-3.678083455709408</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>1.190183370618488</v>
       </c>
       <c r="E60">
-        <v>-16.06350470314406</v>
+        <v>-13.37587802196174</v>
       </c>
       <c r="F60">
-        <v>-2.529650297833776</v>
+        <v>-1.377516324017487</v>
       </c>
       <c r="G60">
-        <v>-7.140536687595593</v>
+        <v>-4.587205608430826</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.7362240206742556</v>
       </c>
       <c r="E61">
-        <v>-15.73885387306017</v>
+        <v>-13.19373826889924</v>
       </c>
       <c r="F61">
-        <v>-2.352884149382987</v>
+        <v>-1.491584172117784</v>
       </c>
       <c r="G61">
-        <v>-7.632202358360453</v>
+        <v>-4.319207015390205</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.3077654531749937</v>
       </c>
       <c r="E62">
-        <v>-15.98303824850177</v>
+        <v>-12.88486464225806</v>
       </c>
       <c r="F62">
-        <v>-2.052986985077871</v>
+        <v>-1.545305454924138</v>
       </c>
       <c r="G62">
-        <v>-7.291696196918715</v>
+        <v>-4.058991514912412</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.07880504585138566</v>
       </c>
       <c r="E63">
-        <v>-16.51687740689599</v>
+        <v>-12.26449993099929</v>
       </c>
       <c r="F63">
-        <v>-2.280616548795356</v>
+        <v>-1.73136671400174</v>
       </c>
       <c r="G63">
-        <v>-7.111347607575839</v>
+        <v>-4.48920683937732</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.4116931097790834</v>
       </c>
       <c r="E64">
-        <v>-16.34350477951233</v>
+        <v>-12.55566269579646</v>
       </c>
       <c r="F64">
-        <v>-2.44998371960434</v>
+        <v>-1.860939943147639</v>
       </c>
       <c r="G64">
-        <v>-7.329009355691841</v>
+        <v>-4.650797877694687</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6823587894958457</v>
       </c>
       <c r="E65">
-        <v>-15.4836517203579</v>
+        <v>-12.18685018718976</v>
       </c>
       <c r="F65">
-        <v>-2.701710491069262</v>
+        <v>-1.966085445952383</v>
       </c>
       <c r="G65">
-        <v>-7.467118694499156</v>
+        <v>-3.938242676913034</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-0.8801842992370195</v>
       </c>
       <c r="E66">
-        <v>-16.36062241126132</v>
+        <v>-12.38960355393519</v>
       </c>
       <c r="F66">
-        <v>-2.474816517605463</v>
+        <v>-1.756160578734932</v>
       </c>
       <c r="G66">
-        <v>-8.534024758167778</v>
+        <v>-4.539007375924577</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.000460604541043</v>
       </c>
       <c r="E67">
-        <v>-14.10260300223868</v>
+        <v>-11.38882438366206</v>
       </c>
       <c r="F67">
-        <v>-2.130330821109858</v>
+        <v>-1.797056249043741</v>
       </c>
       <c r="G67">
-        <v>-8.274676620621273</v>
+        <v>-4.905213302387676</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.043596744031313</v>
       </c>
       <c r="E68">
-        <v>-16.25218357267365</v>
+        <v>-12.07347078345972</v>
       </c>
       <c r="F68">
-        <v>-2.509836577926215</v>
+        <v>-1.912101570679342</v>
       </c>
       <c r="G68">
-        <v>-8.378048405085016</v>
+        <v>-4.774499722315094</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-1.010219179594605</v>
       </c>
       <c r="E69">
-        <v>-14.77439759280256</v>
+        <v>-11.55885046875405</v>
       </c>
       <c r="F69">
-        <v>-2.526098258410572</v>
+        <v>-1.80656590682788</v>
       </c>
       <c r="G69">
-        <v>-7.494225441374708</v>
+        <v>-4.731300413573144</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.9055418485705755</v>
       </c>
       <c r="E70">
-        <v>-15.38307884112155</v>
+        <v>-11.38122107580318</v>
       </c>
       <c r="F70">
-        <v>-1.852038307037156</v>
+        <v>-2.18053651265873</v>
       </c>
       <c r="G70">
-        <v>-8.568000887037318</v>
+        <v>-4.225147795528432</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.7402943472036274</v>
       </c>
       <c r="E71">
-        <v>-14.07666843159675</v>
+        <v>-11.81809202027116</v>
       </c>
       <c r="F71">
-        <v>-3.051257512395972</v>
+        <v>-2.005286276555064</v>
       </c>
       <c r="G71">
-        <v>-7.748296569331615</v>
+        <v>-4.240614664287907</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.5251913040228295</v>
       </c>
       <c r="E72">
-        <v>-16.02200576733777</v>
+        <v>-11.68012753115347</v>
       </c>
       <c r="F72">
-        <v>-2.856033681476004</v>
+        <v>-2.397651608932481</v>
       </c>
       <c r="G72">
-        <v>-7.216785172456087</v>
+        <v>-4.385755601820635</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-0.2714475478250044</v>
       </c>
       <c r="E73">
-        <v>-15.62338684281259</v>
+        <v>-11.78428243332989</v>
       </c>
       <c r="F73">
-        <v>-2.816140335724583</v>
+        <v>-2.025371700970744</v>
       </c>
       <c r="G73">
-        <v>-7.58165694906686</v>
+        <v>-4.705590716915164</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.007775784872416884</v>
       </c>
       <c r="E74">
-        <v>-15.88660892298244</v>
+        <v>-12.26510674651631</v>
       </c>
       <c r="F74">
-        <v>-2.788815808575838</v>
+        <v>-2.214094504513541</v>
       </c>
       <c r="G74">
-        <v>-6.827878835230204</v>
+        <v>-4.531250767726064</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.3012210331371036</v>
       </c>
       <c r="E75">
-        <v>-16.01423943441462</v>
+        <v>-13.14259821193061</v>
       </c>
       <c r="F75">
-        <v>-2.821029360135905</v>
+        <v>-2.475622519088387</v>
       </c>
       <c r="G75">
-        <v>-7.456044919670294</v>
+        <v>-4.045332204017379</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.6009243023533215</v>
       </c>
       <c r="E76">
-        <v>-17.84139718397747</v>
+        <v>-13.19796333514839</v>
       </c>
       <c r="F76">
-        <v>-2.697117193820739</v>
+        <v>-2.370545770778075</v>
       </c>
       <c r="G76">
-        <v>-7.419076057633252</v>
+        <v>-3.993581756147492</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.900479212378982</v>
       </c>
       <c r="E77">
-        <v>-17.3427170977788</v>
+        <v>-13.61365007820848</v>
       </c>
       <c r="F77">
-        <v>-3.090290184415885</v>
+        <v>-2.404374638773601</v>
       </c>
       <c r="G77">
-        <v>-6.962406163764028</v>
+        <v>-4.04610025058249</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.195115266964493</v>
       </c>
       <c r="E78">
-        <v>-17.9836410810324</v>
+        <v>-13.77114587572125</v>
       </c>
       <c r="F78">
-        <v>-2.882108202213924</v>
+        <v>-2.368199005925944</v>
       </c>
       <c r="G78">
-        <v>-7.182954707590275</v>
+        <v>-3.774357430536953</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.485713272819853</v>
       </c>
       <c r="E79">
-        <v>-18.27755715802624</v>
+        <v>-14.005381193768</v>
       </c>
       <c r="F79">
-        <v>-2.961121198562552</v>
+        <v>-2.314916757843075</v>
       </c>
       <c r="G79">
-        <v>-6.185239045692421</v>
+        <v>-3.856015346808617</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.774836667794595</v>
       </c>
       <c r="E80">
-        <v>-18.97243790908123</v>
+        <v>-15.21893977223953</v>
       </c>
       <c r="F80">
-        <v>-2.695834052713802</v>
+        <v>-2.604224901638205</v>
       </c>
       <c r="G80">
-        <v>-6.40109654648952</v>
+        <v>-3.922411648144239</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.062336599679088</v>
       </c>
       <c r="E81">
-        <v>-18.48175963645412</v>
+        <v>-16.08145557411047</v>
       </c>
       <c r="F81">
-        <v>-2.868672082940516</v>
+        <v>-2.673262697722321</v>
       </c>
       <c r="G81">
-        <v>-5.662871375596359</v>
+        <v>-2.897235010998131</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.353309085581712</v>
       </c>
       <c r="E82">
-        <v>-20.05928072787013</v>
+        <v>-16.46879406988255</v>
       </c>
       <c r="F82">
-        <v>-2.98656201823733</v>
+        <v>-2.622033144063589</v>
       </c>
       <c r="G82">
-        <v>-6.2104091234275</v>
+        <v>-2.963611449060518</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>2.650116771319904</v>
       </c>
       <c r="E83">
-        <v>-21.5000419042545</v>
+        <v>-16.53615059227263</v>
       </c>
       <c r="F83">
-        <v>-3.032143762943776</v>
+        <v>-2.719305014704723</v>
       </c>
       <c r="G83">
-        <v>-6.673438575277664</v>
+        <v>-3.740679250765948</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>2.949703366825668</v>
       </c>
       <c r="E84">
-        <v>-23.08362209389278</v>
+        <v>-18.32563143809167</v>
       </c>
       <c r="F84">
-        <v>-3.522141305782545</v>
+        <v>-2.497579225466991</v>
       </c>
       <c r="G84">
-        <v>-6.095367665937825</v>
+        <v>-3.028273024533563</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.249266708040447</v>
       </c>
       <c r="E85">
-        <v>-21.18310306540567</v>
+        <v>-19.3261796561904</v>
       </c>
       <c r="F85">
-        <v>-3.291141943470473</v>
+        <v>-2.778756114836241</v>
       </c>
       <c r="G85">
-        <v>-6.097807538000269</v>
+        <v>-2.764379507961639</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>3.543555692738087</v>
       </c>
       <c r="E86">
-        <v>-22.78050868618936</v>
+        <v>-20.43335985174775</v>
       </c>
       <c r="F86">
-        <v>-3.034787083326109</v>
+        <v>-2.665586217000578</v>
       </c>
       <c r="G86">
-        <v>-5.109212429063106</v>
+        <v>-2.248589891852109</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>3.821600946937378</v>
       </c>
       <c r="E87">
-        <v>-25.4804256458285</v>
+        <v>-22.08984847290952</v>
       </c>
       <c r="F87">
-        <v>-3.825209460505578</v>
+        <v>-3.186349325179321</v>
       </c>
       <c r="G87">
-        <v>-5.338163137468023</v>
+        <v>-2.431633265263953</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.069620890795117</v>
       </c>
       <c r="E88">
-        <v>-25.19903532793988</v>
+        <v>-23.04105896669469</v>
       </c>
       <c r="F88">
-        <v>-3.557681580832255</v>
+        <v>-2.842350708716562</v>
       </c>
       <c r="G88">
-        <v>-5.592148191240909</v>
+        <v>-2.875544316624826</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>4.274986838192635</v>
       </c>
       <c r="E89">
-        <v>-29.08586532498942</v>
+        <v>-24.57512935000711</v>
       </c>
       <c r="F89">
-        <v>-3.330349401012376</v>
+        <v>-2.859992449293983</v>
       </c>
       <c r="G89">
-        <v>-5.176002685317903</v>
+        <v>-2.402699097250723</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>4.4219901024307</v>
       </c>
       <c r="E90">
-        <v>-27.74313202544909</v>
+        <v>-25.63731915629825</v>
       </c>
       <c r="F90">
-        <v>-3.738601163440681</v>
+        <v>-2.915104560969637</v>
       </c>
       <c r="G90">
-        <v>-4.733429094354895</v>
+        <v>-2.475037827829337</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>4.49424557621527</v>
       </c>
       <c r="E91">
-        <v>-28.88831970335281</v>
+        <v>-27.59539961789686</v>
       </c>
       <c r="F91">
-        <v>-3.188880815962276</v>
+        <v>-3.092483701298498</v>
       </c>
       <c r="G91">
-        <v>-4.537203128605674</v>
+        <v>-2.562651415526149</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>4.482031081896391</v>
       </c>
       <c r="E92">
-        <v>-31.91217199418264</v>
+        <v>-29.624051818431</v>
       </c>
       <c r="F92">
-        <v>-3.751988409037324</v>
+        <v>-3.236437388556996</v>
       </c>
       <c r="G92">
-        <v>-5.371122928857007</v>
+        <v>-2.94370844927842</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>4.377309332448886</v>
       </c>
       <c r="E93">
-        <v>-34.24560408085502</v>
+        <v>-31.24487870678237</v>
       </c>
       <c r="F93">
-        <v>-3.740807934201739</v>
+        <v>-3.315773448192715</v>
       </c>
       <c r="G93">
-        <v>-5.432629554431127</v>
+        <v>-2.599722904474908</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>4.175137968970982</v>
       </c>
       <c r="E94">
-        <v>-34.62806088164682</v>
+        <v>-32.95446368568408</v>
       </c>
       <c r="F94">
-        <v>-3.652098897403343</v>
+        <v>-3.558779167640965</v>
       </c>
       <c r="G94">
-        <v>-6.09825777219361</v>
+        <v>-2.885022408503759</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>3.880851384034482</v>
       </c>
       <c r="E95">
-        <v>-37.05543163313432</v>
+        <v>-35.37218425906122</v>
       </c>
       <c r="F95">
-        <v>-3.779655880290828</v>
+        <v>-3.608206193831205</v>
       </c>
       <c r="G95">
-        <v>-5.98905611703521</v>
+        <v>-2.876911571932545</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.500282132906757</v>
       </c>
       <c r="E96">
-        <v>-38.4318431938697</v>
+        <v>-37.32963073429876</v>
       </c>
       <c r="F96">
-        <v>-3.528289448646123</v>
+        <v>-3.537590357844756</v>
       </c>
       <c r="G96">
-        <v>-6.148180798925819</v>
+        <v>-3.564634370624124</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.052366677769521</v>
       </c>
       <c r="E97">
-        <v>-40.94925812252571</v>
+        <v>-38.35801095364864</v>
       </c>
       <c r="F97">
-        <v>-3.906874060910567</v>
+        <v>-4.091658805820455</v>
       </c>
       <c r="G97">
-        <v>-6.355235559133996</v>
+        <v>-3.179339838581586</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.54401000791455</v>
       </c>
       <c r="E98">
-        <v>-43.69184236426511</v>
+        <v>-41.47538755392187</v>
       </c>
       <c r="F98">
-        <v>-4.802588561925075</v>
+        <v>-4.312045124967861</v>
       </c>
       <c r="G98">
-        <v>-7.588479983423299</v>
+        <v>-3.64373323519393</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.016603087332644</v>
       </c>
       <c r="E99">
-        <v>-44.65763907282899</v>
+        <v>-43.97796946596576</v>
       </c>
       <c r="F99">
-        <v>-4.572558389474278</v>
+        <v>-4.277119498531029</v>
       </c>
       <c r="G99">
-        <v>-6.699002607931916</v>
+        <v>-4.729264428066492</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>1.463687228024995</v>
       </c>
       <c r="E100">
-        <v>-47.30247620311282</v>
+        <v>-45.54566150454812</v>
       </c>
       <c r="F100">
-        <v>-4.831216110998423</v>
+        <v>-4.721502161967241</v>
       </c>
       <c r="G100">
-        <v>-7.646225829264806</v>
+        <v>-4.947866371115647</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>0.9494258362747091</v>
       </c>
       <c r="E101">
-        <v>-48.39342408358968</v>
+        <v>-47.51215360661598</v>
       </c>
       <c r="F101">
-        <v>-5.102941328301731</v>
+        <v>-4.583313083464824</v>
       </c>
       <c r="G101">
-        <v>-7.658094135023093</v>
+        <v>-5.39191646538917</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>0.4227451129601721</v>
       </c>
       <c r="E102">
-        <v>-51.07769176917681</v>
+        <v>-50.44712327386025</v>
       </c>
       <c r="F102">
-        <v>-5.063687482185271</v>
+        <v>-4.817438704355062</v>
       </c>
       <c r="G102">
-        <v>-8.288037982417771</v>
+        <v>-5.193846525774575</v>
       </c>
     </row>
   </sheetData>
